--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5131,79 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D45-625/LB</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>625</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2382x1134x30</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>45</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ficha técnica oficial JAM66D45-625/LB. Alpha_Isc=+0.045%/°C. Bifacial 80%±5%. Peso=33.1kg. Vmax=1500V. IEC61215/61730.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>N-Type Bifacial</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="M62" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="N62" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="O62" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>132</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ficha oficial JA Solar JAM66D45 LB Deep Blue 4.0</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5204,6 +5204,79 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-320 Luminous PV Bifacial</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>320</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2088x1128x5</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>45</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I63" t="n">
+        <v>45</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Panel BIPV semi-transparente τ=45%. Frameless doble vidrio 2+2mm. Mono half-cell 182mm. Alpha_Isc=+0.045%/°C. Vmax=700Vdc IEC/UL. Certificado IEC61215/61730. 30 años garantía. einnova-solarline.com</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Mono PERC Bifacial BIPV</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="M63" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N63" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="O63" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>80</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S63" t="n">
+        <v>104</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-32 Luminous PV — 2x40 half-cells 182mm</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5277,6 +5277,79 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-620M TopCon N-Type Black</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>620</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2278x1134x30</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>45</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Datos eléctricos: ficha oficial EINNOVA ESM-620M TopCon N-Type Black. Alpha_Isc=+0.046%/°C. Vmax=1500Vdc. Eficiencia=23.99%. DIMENSIONES ESTIMADAS (2278x1134) — confirmar con EINNOVA. Precio pendiente.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Mono</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="M64" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="N64" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="O64" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>132</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S64" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ficha EINNOVA ESM-620M — Ns y dims estimados (confirmar con fabricante)</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2278x1134x30</t>
+          <t>2279x1134x30</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Datos eléctricos: ficha oficial EINNOVA ESM-620M TopCon N-Type Black. Alpha_Isc=+0.046%/°C. Vmax=1500Vdc. Eficiencia=23.99%. DIMENSIONES ESTIMADAS (2278x1134) — confirmar con EINNOVA. Precio pendiente.</t>
+          <t>Datos eléctricos y mecánicos: ficha oficial EINNOVA ESM-620M TopCon N-Type Black. Dims confirmadas: 2279×1134×30mm. Célula 183.75×183.75mm monocristalino N-Type. Alpha_Isc=+0.046%/°C. Vmax=1500Vdc. Eficiencia=23.99%. Precio pendiente.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Ficha EINNOVA ESM-620M — Ns y dims estimados (confirmar con fabricante)</t>
+          <t>Ficha EINNOVA ESM-620M — célula 183.75×183.75mm MonoC N-Type</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V64"/>
+  <dimension ref="A1:V69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5350,6 +5350,371 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-530T TopCon Bifacial</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>530</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2094x1134x30</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>45</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-530T TopCon Bifacial. Efic=22.32%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Mono</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>39</v>
+      </c>
+      <c r="N65" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O65" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>132</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S65" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-535T TopCon Bifacial</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>535</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2094x1134x30</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>45</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-535T TopCon Bifacial. Efic=22.52%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Mono</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="M66" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="O66" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>132</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S66" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-540T TopCon Bifacial</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>540</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2094x1134x30</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>45</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-540T TopCon Bifacial. Efic=22.74%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Mono</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="O67" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>132</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S67" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-545T TopCon Bifacial</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>545</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2094x1134x30</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>45</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-545T TopCon Bifacial. Efic=22.95%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Mono</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="M68" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="N68" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="O68" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>132</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S68" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-550T TopCon Bifacial</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>550</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2094x1134x30</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>45</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-550T TopCon Bifacial. Efic=23.16%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Mono</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N69" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="O69" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>132</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S69" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -5380,7 +5380,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-530T TopCon Bifacial. Efic=22.32%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+          <t>Ficha oficial EINNOVA ESM-530T TopCon Bifacial. Efic=22.32%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims CONFIRMADAS: 2094×1134×30mm. 132 semicélulas 6×22.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+          <t>Ficha oficial EINNOVA ESM-T — 132 piezas (6×22) confirmadas</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-535T TopCon Bifacial. Efic=22.52%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+          <t>Ficha oficial EINNOVA ESM-535T TopCon Bifacial. Efic=22.52%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims CONFIRMADAS: 2094×1134×30mm. 132 semicélulas 6×22.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+          <t>Ficha oficial EINNOVA ESM-T — 132 piezas (6×22) confirmadas</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-540T TopCon Bifacial. Efic=22.74%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+          <t>Ficha oficial EINNOVA ESM-540T TopCon Bifacial. Efic=22.74%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims CONFIRMADAS: 2094×1134×30mm. 132 semicélulas 6×22.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+          <t>Ficha oficial EINNOVA ESM-T — 132 piezas (6×22) confirmadas</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-545T TopCon Bifacial. Efic=22.95%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+          <t>Ficha oficial EINNOVA ESM-545T TopCon Bifacial. Efic=22.95%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims CONFIRMADAS: 2094×1134×30mm. 132 semicélulas 6×22.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+          <t>Ficha oficial EINNOVA ESM-T — 132 piezas (6×22) confirmadas</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-550T TopCon Bifacial. Efic=23.16%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims ESTIMADAS — confirmar con EINNOVA.</t>
+          <t>Ficha oficial EINNOVA ESM-550T TopCon Bifacial. Efic=23.16%. CoefIsc=+0.04%/°C. Vmax=1500Vdc. Dims CONFIRMADAS: 2094×1134×30mm. 132 semicélulas 6×22.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-T series — Ns estimado (confirmar dims)</t>
+          <t>Ficha oficial EINNOVA ESM-T — 132 piezas (6×22) confirmadas</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5715,6 +5715,79 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EINNOVA Agri ESM-305HE Bifacial</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>305</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1762x1134x30</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>45</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I70" t="n">
+        <v>38</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA Agri ESM-305HE. Panel agrícola semitransparente τ=38%. TOPCon N-Type 182×105mm (4×16pcs=64 celdas). Dual glass 2+2mm. Marco: fibra vidrio reforzada con poliuretano. Vmax=1500Vdc. CoefIsc=+0.045%/°C. IEC61215/61730. Agrivoltaico/BIPV.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Bifacial Agri</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="M70" t="n">
+        <v>20</v>
+      </c>
+      <c r="N70" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="O70" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>64</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S70" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-305HE — 4×16 celdas TOPCon 182×105mm</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5788,6 +5788,79 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-400 Terra Cotta TopCon</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>400</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1762x1134x30</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>45</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-400 Terra Cotta. Panel BIPV decorativo con vidrio color terracota — OPACO (τ=0%). TOPCon N-Type Monocristalino. CoefIsc=+0.046%/°C. Tolerancia 0~+3%. Vmax=1500Vdc. Dims y Ns ESTIMADOS (confirmar con EINNOVA). Precio pendiente.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>N-Type TopCon Mono Colored Glass</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="O71" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>54</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S71" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ficha oficial EINNOVA ESM-400 Terracota — Ns estimado (confirmar con fabricante)</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -5804,7 +5804,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1762x1134x30</t>
+          <t>1722x1134x30</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-400 Terra Cotta. Panel BIPV decorativo con vidrio color terracota — OPACO (τ=0%). TOPCon N-Type Monocristalino. CoefIsc=+0.046%/°C. Tolerancia 0~+3%. Vmax=1500Vdc. Dims y Ns ESTIMADOS (confirmar con EINNOVA). Precio pendiente.</t>
+          <t>Ficha oficial EINNOVA ESM-400 Terra Cotta. Panel BIPV decorativo vidrio color terracota — OPACO (τ=0%). TOPCon N-Type 182×93.4mm half-cells. 108 piezas (6×18) → N_s=54 en serie. Dims CONFIRMADAS: 1722×1134×30mm. CoefIsc=+0.046%/°C. Vmax=1500Vdc. Precio pendiente.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Ficha oficial EINNOVA ESM-400 Terracota — Ns estimado (confirmar con fabricante)</t>
+          <t>Ficha oficial EINNOVA ESM-400 — 108 semicélulas (6×18) 182×93.4mm → N_s=54 en serie</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5861,6 +5861,76 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EINNOVA Solarline</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-FT 120W Flat Tile Color</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>120</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1600x460x6</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>EINNOVA ESM-FT 120W — Teja solar plana doble vidrio BIPV. Colores: negro, gris, rojo/terracota. OPACA (τ=0%). Dims CONFIRMADAS: 1600×460×6mm. Peso 13.5kg. Vmax=1000Vdc. Fusible 20A. Efic. 21.8% = eficiencia de celda (módulo=16.3% sobre área total). Ficha STC indica 20°C celda (no estándar — asumido 25°C). CoefT_C y CoefVoc_C ESTIMADOS para N-Type TOPCon. N_s ESTIMADO. Nota: módulo pequeño (120W) — requiere más unidades en serie por string. Precio pendiente.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Double Glass BIPV Tile</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M72" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="N72" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="O72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>15</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S72" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>N_s ESTIMADO: 10.99V / 0.73V célula TOPCon ≈ 15. Confirmar con EINNOVA</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5931,6 +5931,378 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-715/LB</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>715</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>45</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="M73" t="n">
+        <v>41</v>
+      </c>
+      <c r="N73" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="O73" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>66</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-720/LB</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>720</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>45</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>49</v>
+      </c>
+      <c r="M74" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="N74" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="O74" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>66</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-725/LB</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>725</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>45</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="O75" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>66</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-730/LB</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>730</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>45</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="M76" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="N76" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="O76" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>66</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-735/LB</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>735</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>45</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="N77" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O77" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>66</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JA Solar</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>JA Solar JAM66D46-740/LB</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>740</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2384x1303x33 mm</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>45</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>N-Type n-Bycium+ 18BB Half-Cut Double Glass Bifacial. Max sys voltage 1500 VDC. Bifacialidad 80%±5%. 0.4% degradación anual (30 años). NOCT 45±2°C.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>N-Type TOPCon Bifacial</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="N78" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="O78" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>66</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -5112,7 +5112,7 @@
         <v>-0.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="R61" t="n">
         <v>1.3</v>
@@ -5185,7 +5185,7 @@
         <v>-0.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="R62" t="n">
         <v>1.3</v>
@@ -5331,7 +5331,7 @@
         <v>-0.26</v>
       </c>
       <c r="Q64" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="R64" t="n">
         <v>1.3</v>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catalogo_Paneles_FV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Paneles_FV" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:W78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,6 +610,11 @@
           <t>Confianza</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>BifacialidadPct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5992,6 +5997,9 @@
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
       </c>
+      <c r="W73" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -6054,6 +6062,9 @@
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
       </c>
+      <c r="W74" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -6116,6 +6127,9 @@
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
       </c>
+      <c r="W75" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -6178,6 +6192,9 @@
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
       </c>
+      <c r="W76" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -6240,6 +6257,9 @@
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
       </c>
+      <c r="W77" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -6301,6 +6321,9 @@
         <is>
           <t>Alta — ficha oficial JA Solar Global-EN-20250709C</t>
         </is>
+      </c>
+      <c r="W78" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W78"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6326,6 +6326,79 @@
         <v>80</v>
       </c>
     </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Suntech</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Suntech STP-410-A72-Pnh-Bifacial</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>410</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2028x1002x35 mm</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Modulo bifacial Suntech STP-410-A72-Pnh-Bifacial. Silicio monocristalino, half-cut cells (3 submodulos), 72 celdas en serie x 2 strings paralelo. Vmax sistema 1500V (IEC) / 1000V (UL). 3 diodos bypass. Conectores MC4-EVO2. Marco aluminio anodizado, vidrio semitemplado 2mm. Eficiencia modulo 20.19%, eficiencia celda 23.20%. Isc=10.490A verificado. alfa Isc = +0.050 %/degC (5.2 mA/degC) -- SIN COLUMNA en este catalogo para coeficiente de Isc (CoefIsc_C no existe en el schema), queda documentado solo aqui. Parametros SDM PVsyst (no cargados al motor de simulacion -- este catalogo Excel no soporta SDM completo): Rsh(1000W/m2)=1200ohm, Rsh(G-&gt;0)=5000ohm, Rs=0.229ohm, IoRef=0.013nA. Fuente: ficha tecnica extraida y verificada desde base PVsyst V8.1.5 (Datasheets 2020), aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Mono-Si Bifacial</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="O79" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-0.304</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>72</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="S79" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>PVsyst V8.1.5 PAN (Datasheets 2020) -- Gamma=0.97 es dato de fabricante, no estimado</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Alta -- ficha tecnica extraida y verificada desde base PVsyst V8.1.5 (Datasheets 2020), aportada por el usuario (28-ago-2026)</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6399,6 +6399,506 @@
         <v>70</v>
       </c>
     </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Solar First ST1-72</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>72</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>116</v>
+      </c>
+      <c r="M80" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Solar First ST1-64</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>64</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>20</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>116</v>
+      </c>
+      <c r="M81" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Solar First ST1-56</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>56</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>30</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>116</v>
+      </c>
+      <c r="M82" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Solar First ST1-48</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>48</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>40</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>116</v>
+      </c>
+      <c r="M83" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Solar First ST1-40</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>50</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>116</v>
+      </c>
+      <c r="M84" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Solar First ST1-32</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>32</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>60</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>114</v>
+      </c>
+      <c r="M85" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Solar First ST1-24</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>24</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>70</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>114</v>
+      </c>
+      <c r="M86" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Solar First ST1-16</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>16</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>80</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>114</v>
+      </c>
+      <c r="M87" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Solar First ST2-80</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>80</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="M88" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Solar First</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Solar First ST2-85</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>85</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1200x600x6.8 mm</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>CdTe pelicula delgada</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/bipv_python/datos/paneles_catalogo.xlsx
+++ b/bipv_python/datos/paneles_catalogo.xlsx
@@ -6423,7 +6423,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6443,9 +6443,20 @@
       <c r="O80" t="n">
         <v>0.8</v>
       </c>
+      <c r="Q80" t="n">
+        <v>141</v>
+      </c>
+      <c r="S80" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6484,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6493,9 +6504,20 @@
       <c r="O81" t="n">
         <v>0.71</v>
       </c>
+      <c r="Q81" t="n">
+        <v>141</v>
+      </c>
+      <c r="S81" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6545,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6543,9 +6565,20 @@
       <c r="O82" t="n">
         <v>0.62</v>
       </c>
+      <c r="Q82" t="n">
+        <v>141</v>
+      </c>
+      <c r="S82" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6606,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6593,9 +6626,20 @@
       <c r="O83" t="n">
         <v>0.53</v>
       </c>
+      <c r="Q83" t="n">
+        <v>141</v>
+      </c>
+      <c r="S83" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6667,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6643,9 +6687,20 @@
       <c r="O84" t="n">
         <v>0.44</v>
       </c>
+      <c r="Q84" t="n">
+        <v>141</v>
+      </c>
+      <c r="S84" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6728,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6693,9 +6748,20 @@
       <c r="O85" t="n">
         <v>0.36</v>
       </c>
+      <c r="Q85" t="n">
+        <v>141</v>
+      </c>
+      <c r="S85" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6789,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6743,9 +6809,20 @@
       <c r="O86" t="n">
         <v>0.27</v>
       </c>
+      <c r="Q86" t="n">
+        <v>141</v>
+      </c>
+      <c r="S86" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6850,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=141 (NsA=153,69) por analogia real: mismas dimensiones fisicas (1200x600mm) y mismo Voc (~116V) que el panel SolTech ASP-ST1-T40 ya validado en esta app (a_ref=154 calibrado contra VBA, mismo fabricante de vidrio FV CdTe BIPV), asumiendo el mismo pitch de escriba laser CdTe. Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6793,9 +6870,20 @@
       <c r="O87" t="n">
         <v>0.18</v>
       </c>
+      <c r="Q87" t="n">
+        <v>141</v>
+      </c>
+      <c r="S87" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6911,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=72 (NsA=78,48) por analogia real: mismo pitch de escriba laser CdTe que la serie ST1 (ver nota de ST1), pero aproximadamente la mitad de celdas en serie -- consistente con su Voc (~59V) siendo casi exactamente la mitad del Voc de ST1 (~116V) en las mismas dimensiones fisicas (1200x600mm). Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6843,9 +6931,20 @@
       <c r="O88" t="n">
         <v>1.68</v>
       </c>
+      <c r="Q88" t="n">
+        <v>72</v>
+      </c>
+      <c r="S88" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6972,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha -- no se infiere. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
+          <t>Coeficientes de temperatura NO publicados por Solar First. La ficha incluye una referencia TIPICA de la tecnologia CdTe (First Solar Series 4, fabricante distinto, mismas dimensiones fisicas) EXPLICITAMENTE marcada como no confirmada: gamma Pmax=-0.32%/degC, beta Voc=-0.28%/degC, alfa Isc=+0.04%/degC. La propia ficha recomienda NO cargarlos como dato oficial del fabricante -- por eso quedan fuera de los campos numericos de este registro, solo documentados aqui. NOCT tampoco publicado. Ns (celdas en serie) no especificado en la ficha del fabricante -- ESTIMADO el 31-ago-2026 en N_s=72 (NsA=78,48) por analogia real: mismo pitch de escriba laser CdTe que la serie ST1 (ver nota de ST1), pero aproximadamente la mitad de celdas en serie -- consistente con su Voc (~59V) siendo casi exactamente la mitad del Voc de ST1 (~116V) en las mismas dimensiones fisicas (1200x600mm). Con este N_s, Motor IV activa via ajuste cerrado (fit_desoto_batzelis, que no depende del valor exacto de Ns) -- validado reproduciendo Voc/Isc/Vmp/Imp/Pmax de esta misma ficha dentro del margen del 5%%. Dato ESTIMADO, NO confirmado por Solar First -- si se obtiene el N_s real del fabricante, reemplazar aqui. Fuente: ficha de familia Solar First (Xiamen Solar First Energy Technology Co., Ltd.), serie ST1/ST2, aportada por el usuario (28-ago-2026).</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6893,9 +6992,20 @@
       <c r="O89" t="n">
         <v>1.76</v>
       </c>
+      <c r="Q89" t="n">
+        <v>72</v>
+      </c>
+      <c r="S89" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Estimado por analogia con ASP-ST1-T40 (ver Notas)</t>
+        </is>
+      </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Alta (electricos) / ficha de familia del fabricante -- coeficientes de temperatura NO confirmados, ver Notas</t>
+          <t>Estimado -- no confirmado por fabricante</t>
         </is>
       </c>
     </row>
